--- a/Techniques/Correlation drift Detection/outputs/G12/dsas_g12_bearings_vibration_temp_correlation_detection/correlation_detection/dsas_g12_bearings_vibration_temp_correlation_detection_output2.xlsx
+++ b/Techniques/Correlation drift Detection/outputs/G12/dsas_g12_bearings_vibration_temp_correlation_detection/correlation_detection/dsas_g12_bearings_vibration_temp_correlation_detection_output2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,74 +433,74 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>AssetID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9358</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9359</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9360</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9361</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9368</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9369</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9370</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AssetID_12208</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9343</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9344</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>AssetID_9408</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45232.58388888889</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +541,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45232.69068287037</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,7 +582,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45232.81658564815</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -611,7 +623,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45232.939375</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -652,7 +664,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45233.06450231482</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -693,7 +705,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45233.19976851852</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -734,7 +746,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45233.3163425926</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -775,7 +787,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45233.5778125</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -816,7 +828,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45233.70393518519</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45233.81425925926</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -898,7 +910,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>45233.94961805556</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -939,7 +951,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>45234.07908564815</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -980,7 +992,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>45234.205625</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1021,7 +1033,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>45234.32534722222</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1062,7 +1074,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>45234.44539351852</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1103,7 +1115,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>45234.57993055556</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1144,7 +1156,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>45234.69010416666</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1185,7 +1197,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>45234.8234837963</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1226,7 +1238,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>45234.94009259259</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1267,7 +1279,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>45235.07965277778</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1308,7 +1320,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45235.1914699074</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45235.31483796296</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1390,7 +1402,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45235.4407175926</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1431,7 +1443,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45235.56414351852</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1472,7 +1484,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45235.70108796296</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1513,7 +1525,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45235.81854166667</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1554,7 +1566,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45236.22508101852</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1595,7 +1607,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45236.31480324074</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1636,7 +1648,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45236.44541666667</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1677,7 +1689,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45236.6902662037</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1718,7 +1730,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45236.81527777778</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1759,7 +1771,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45236.9453125</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1800,7 +1812,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45237.06493055556</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1841,7 +1853,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45237.19125</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1882,7 +1894,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45237.3155787037</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1923,7 +1935,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45237.44138888889</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1964,7 +1976,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45237.57152777778</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -2005,7 +2017,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>45237.69288194444</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -2046,7 +2058,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>45237.82814814815</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -2087,7 +2099,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45237.94748842593</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -2128,7 +2140,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45238.2062037037</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -2169,7 +2181,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45238.31596064815</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -2210,7 +2222,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45238.44385416667</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -2251,7 +2263,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45238.56461805556</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -2292,7 +2304,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45238.81765046297</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -2333,7 +2345,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45238.94136574074</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -2374,7 +2386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45239.07863425926</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2415,7 +2427,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45239.20971064815</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2456,7 +2468,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45239.31733796297</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2497,7 +2509,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45239.44678240741</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2538,7 +2550,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45239.56444444445</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2579,7 +2591,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45239.69660879629</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2620,7 +2632,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45239.81575231482</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2661,7 +2673,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45239.96009259259</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2702,7 +2714,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45240.07539351852</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2743,7 +2755,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45240.32247685185</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2784,7 +2796,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45240.45472222222</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2825,7 +2837,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45240.56987268518</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2866,7 +2878,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45240.69065972222</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2907,7 +2919,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45240.81402777778</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2948,7 +2960,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45240.93924768519</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2989,7 +3001,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45241.06414351852</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -3030,7 +3042,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45241.19800925926</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -3071,7 +3083,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45241.33342592593</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -3112,7 +3124,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45241.45502314815</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -3153,7 +3165,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45241.56454861111</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -3194,7 +3206,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45241.70119212963</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -3235,7 +3247,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45241.83112268519</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -3276,7 +3288,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45241.9537037037</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -3317,7 +3329,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45242.08201388889</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -3358,7 +3370,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45242.69986111111</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -3399,7 +3411,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45242.81715277778</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -3440,7 +3452,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45242.93877314815</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -3481,7 +3493,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45243.08626157408</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -3522,7 +3534,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45243.31465277778</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -3563,7 +3575,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45243.43993055556</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -3604,7 +3616,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45243.56521990741</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3645,7 +3657,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45243.69731481482</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3686,7 +3698,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45243.85986111111</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3727,7 +3739,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45244.03325231482</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3768,7 +3780,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45244.36030092592</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3809,7 +3821,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45244.52890046296</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3850,7 +3862,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45244.70230324074</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3891,7 +3903,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45244.85921296296</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3932,7 +3944,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45245.02326388889</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3973,7 +3985,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45245.20512731482</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -4014,7 +4026,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45245.35769675926</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -4055,7 +4067,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45245.5274537037</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -4096,7 +4108,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45245.69355324074</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -4137,7 +4149,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45246.03002314815</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -4178,7 +4190,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45246.21109953704</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -4219,7 +4231,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45246.35756944444</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -4260,7 +4272,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45246.52885416667</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -4301,7 +4313,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45246.70027777777</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -4342,7 +4354,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45246.85549768519</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -4383,7 +4395,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45247.03329861111</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -4424,7 +4436,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45247.35915509259</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -4465,7 +4477,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45247.53670138889</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -4506,7 +4518,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45247.69616898148</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -4547,7 +4559,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45247.86167824074</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -4588,7 +4600,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45248.03383101852</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -4629,7 +4641,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45248.22371527777</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -4670,7 +4682,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45248.36859953704</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -4711,7 +4723,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45248.53355324074</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -4752,7 +4764,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45248.69059027778</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -4793,7 +4805,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45248.85614583334</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -4834,7 +4846,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45249.20056712963</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -4875,7 +4887,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45249.36881944445</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45249.54421296297</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -4957,7 +4969,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45249.7016087963</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -4998,7 +5010,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45249.85693287037</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -5039,7 +5051,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45250.02412037037</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -5080,7 +5092,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45250.20712962963</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -5121,7 +5133,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45250.52333333333</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -5162,7 +5174,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45251.205625</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -5203,7 +5215,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45251.36144675926</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -5244,7 +5256,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>45251.52275462963</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -5285,7 +5297,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>45251.89483796297</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -5326,7 +5338,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>45252.02288194445</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -5367,7 +5379,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>45252.21390046296</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -5408,7 +5420,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>45252.52262731481</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -5449,7 +5461,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45252.68975694444</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -5490,7 +5502,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45253.19027777778</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -5531,7 +5543,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45253.35717592593</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -5572,7 +5584,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45253.52355324074</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -5613,7 +5625,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45253.69</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -5654,7 +5666,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45253.86288194444</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -5695,7 +5707,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45254.03780092593</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -5736,7 +5748,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45254.19773148148</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -5777,7 +5789,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45254.35577546297</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -5818,7 +5830,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45254.52780092593</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -5859,7 +5871,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45254.68921296296</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -5900,7 +5912,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45254.86484953704</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -5941,7 +5953,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45255.03583333334</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -5982,7 +5994,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45255.20597222223</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -6023,7 +6035,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45255.35901620371</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -6064,7 +6076,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45255.52479166666</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -6105,7 +6117,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45255.68916666666</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -6146,7 +6158,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45255.85908564815</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -6187,7 +6199,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45256.02885416667</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -6228,7 +6240,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45256.35721064815</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -6269,7 +6281,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45256.52245370371</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -6310,7 +6322,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45256.69059027778</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -6351,7 +6363,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45256.85734953704</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -6392,7 +6404,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45257.03400462963</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -6433,7 +6445,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45257.19155092593</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -6474,7 +6486,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45257.35650462963</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -6515,7 +6527,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45257.53321759259</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -6556,7 +6568,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45257.70081018518</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -6597,7 +6609,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45257.86366898148</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -6638,7 +6650,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45258.02313657408</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -6679,7 +6691,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45258.20119212963</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -6720,7 +6732,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45258.37204861111</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -6761,7 +6773,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45258.52905092593</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -6802,7 +6814,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>45258.85935185185</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -6843,7 +6855,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>45259.04449074074</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -6884,7 +6896,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>45259.19268518518</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -6925,7 +6937,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>45259.35609953704</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -6966,7 +6978,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>45259.68962962963</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -7007,7 +7019,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>45260.03945601852</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -7048,7 +7060,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>45260.36225694444</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -7089,7 +7101,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>45260.52806712963</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -7130,7 +7142,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>45260.85832175926</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -7171,7 +7183,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45261.36832175926</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -7212,7 +7224,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45261.704375</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -7253,7 +7265,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45261.86386574074</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -7294,7 +7306,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45262.03394675926</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -7335,7 +7347,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45262.20064814815</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -7376,7 +7388,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45262.3559837963</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -7417,7 +7429,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45262.53416666666</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -7458,7 +7470,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45232.58388888889</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -7499,7 +7511,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45232.69068287037</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -7540,7 +7552,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45232.81658564815</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -7581,7 +7593,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45232.939375</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -7622,7 +7634,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45233.06450231482</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -7663,7 +7675,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45233.19976851852</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -7704,7 +7716,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45233.3163425926</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -7745,7 +7757,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45233.5778125</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -7786,7 +7798,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45233.70393518519</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -7827,7 +7839,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45233.81425925926</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -7868,7 +7880,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45233.94961805556</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -7909,7 +7921,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45234.07908564815</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -7950,7 +7962,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45234.205625</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -7991,7 +8003,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45234.32534722222</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -8032,7 +8044,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45234.44539351852</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -8073,7 +8085,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45234.57993055556</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -8114,7 +8126,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45234.69010416666</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -8155,7 +8167,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45234.8234837963</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -8196,7 +8208,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45234.94009259259</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -8237,7 +8249,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45235.07965277778</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -8278,7 +8290,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45235.1914699074</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -8319,7 +8331,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45235.31483796296</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -8360,7 +8372,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45235.4407175926</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -8401,7 +8413,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45235.56414351852</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -8442,7 +8454,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45235.70108796296</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -8483,7 +8495,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45235.81854166667</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -8524,7 +8536,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>45236.22508101852</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -8565,7 +8577,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>45236.31480324074</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -8606,7 +8618,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>45236.44541666667</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -8647,7 +8659,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>45236.6902662037</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -8688,7 +8700,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>45236.81527777778</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -8729,7 +8741,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>45236.9453125</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -8770,7 +8782,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>45237.06493055556</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -8811,7 +8823,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>45237.19125</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -8852,7 +8864,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>45237.3155787037</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -8893,7 +8905,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>45237.44138888889</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -8934,7 +8946,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45237.57152777778</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -8975,7 +8987,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45237.69288194444</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -9016,7 +9028,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45237.82814814815</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -9057,7 +9069,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45237.94748842593</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -9098,7 +9110,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45238.2062037037</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -9139,7 +9151,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45238.31596064815</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -9180,7 +9192,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45238.44385416667</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -9221,7 +9233,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45238.56461805556</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -9262,7 +9274,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45238.81765046297</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -9303,7 +9315,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45238.94136574074</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -9344,7 +9356,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45239.07863425926</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -9385,7 +9397,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45239.20971064815</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -9426,7 +9438,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45239.31733796297</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -9467,7 +9479,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45239.44678240741</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -9508,7 +9520,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45239.56444444445</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -9549,7 +9561,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45239.69660879629</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -9590,7 +9602,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45239.81575231482</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -9631,7 +9643,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45239.96009259259</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -9672,7 +9684,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45240.07539351852</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -9713,7 +9725,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45240.32247685185</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -9754,7 +9766,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45240.45472222222</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -9795,7 +9807,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45240.56987268518</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -9836,7 +9848,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45240.69065972222</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -9877,7 +9889,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45240.81402777778</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -9918,7 +9930,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45240.93924768519</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -9959,7 +9971,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45241.06414351852</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -10000,7 +10012,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45241.19800925926</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -10041,7 +10053,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45241.33342592593</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -10082,7 +10094,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45241.45502314815</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -10123,7 +10135,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45241.56454861111</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -10164,7 +10176,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45241.70119212963</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -10205,7 +10217,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45241.83112268519</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -10246,7 +10258,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45241.9537037037</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -10287,7 +10299,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>45242.08201388889</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -10328,7 +10340,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>45242.69986111111</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -10369,7 +10381,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>45242.81715277778</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -10410,7 +10422,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>45242.93877314815</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -10451,7 +10463,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>45243.08626157408</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -10492,7 +10504,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>45243.31465277778</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -10533,7 +10545,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>45243.43993055556</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -10574,7 +10586,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>45243.56521990741</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -10615,7 +10627,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>45243.69731481482</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -10656,7 +10668,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>45243.85986111111</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -10697,7 +10709,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>45244.03325231482</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -10738,7 +10750,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>45244.36030092592</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -10779,7 +10791,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>45244.52890046296</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -10820,7 +10832,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>45244.70230324074</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -10861,7 +10873,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>45244.85921296296</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -10902,7 +10914,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>45245.02326388889</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -10943,7 +10955,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>45245.20512731482</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -10984,7 +10996,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>45245.35769675926</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -11025,7 +11037,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>45245.5274537037</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -11066,7 +11078,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>45245.69355324074</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -11107,7 +11119,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>45246.03002314815</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -11148,7 +11160,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>45246.21109953704</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -11189,7 +11201,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>45246.35756944444</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -11230,7 +11242,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>45246.52885416667</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -11271,7 +11283,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>45246.70027777777</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -11312,7 +11324,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>45246.85549768519</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -11353,7 +11365,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>45247.03329861111</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -11394,7 +11406,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>45247.35915509259</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -11435,7 +11447,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>45247.53670138889</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -11476,7 +11488,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>45247.69616898148</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -11517,7 +11529,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>45247.86167824074</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -11558,7 +11570,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>45248.03383101852</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -11599,7 +11611,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>45248.22371527777</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -11640,7 +11652,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>45248.36859953704</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -11681,7 +11693,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>45248.53355324074</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -11722,7 +11734,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>45248.69059027778</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -11763,7 +11775,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>45248.85614583334</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -11804,7 +11816,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>45249.20056712963</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -11845,7 +11857,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>45249.36881944445</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -11886,7 +11898,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>45249.54421296297</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -11927,7 +11939,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>45249.7016087963</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -11968,7 +11980,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>45249.85693287037</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -12009,7 +12021,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>45250.02412037037</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -12050,7 +12062,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>45250.20712962963</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -12091,7 +12103,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>45250.52333333333</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -12132,7 +12144,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>45251.205625</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -12173,7 +12185,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>45251.36144675926</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -12214,7 +12226,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>45251.52275462963</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -12255,7 +12267,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>45251.89483796297</v>
       </c>
       <c r="B289" t="inlineStr">
@@ -12296,7 +12308,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>45252.02288194445</v>
       </c>
       <c r="B290" t="inlineStr">
@@ -12337,7 +12349,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>45252.21390046296</v>
       </c>
       <c r="B291" t="inlineStr">
@@ -12378,7 +12390,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>45252.52262731481</v>
       </c>
       <c r="B292" t="inlineStr">
@@ -12419,7 +12431,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>45252.68975694444</v>
       </c>
       <c r="B293" t="inlineStr">
@@ -12460,7 +12472,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>45253.19027777778</v>
       </c>
       <c r="B294" t="inlineStr">
@@ -12501,7 +12513,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>45253.35717592593</v>
       </c>
       <c r="B295" t="inlineStr">
@@ -12542,7 +12554,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>45253.52355324074</v>
       </c>
       <c r="B296" t="inlineStr">
@@ -12583,7 +12595,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>45253.69</v>
       </c>
       <c r="B297" t="inlineStr">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>45253.86288194444</v>
       </c>
       <c r="B298" t="inlineStr">
@@ -12665,7 +12677,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>45254.03780092593</v>
       </c>
       <c r="B299" t="inlineStr">
@@ -12706,7 +12718,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>45254.19773148148</v>
       </c>
       <c r="B300" t="inlineStr">
@@ -12747,7 +12759,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>45254.35577546297</v>
       </c>
       <c r="B301" t="inlineStr">
@@ -12788,7 +12800,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>45254.52780092593</v>
       </c>
       <c r="B302" t="inlineStr">
@@ -12829,7 +12841,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>45254.68921296296</v>
       </c>
       <c r="B303" t="inlineStr">
@@ -12870,7 +12882,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>45254.86484953704</v>
       </c>
       <c r="B304" t="inlineStr">
@@ -12911,7 +12923,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>45255.03583333334</v>
       </c>
       <c r="B305" t="inlineStr">
@@ -12952,7 +12964,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>45255.20597222223</v>
       </c>
       <c r="B306" t="inlineStr">
@@ -12993,7 +13005,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>45255.35901620371</v>
       </c>
       <c r="B307" t="inlineStr">
@@ -13034,7 +13046,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>45255.52479166666</v>
       </c>
       <c r="B308" t="inlineStr">
@@ -13075,7 +13087,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>45255.68916666666</v>
       </c>
       <c r="B309" t="inlineStr">
@@ -13116,7 +13128,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>45255.85908564815</v>
       </c>
       <c r="B310" t="inlineStr">
@@ -13157,7 +13169,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>45256.02885416667</v>
       </c>
       <c r="B311" t="inlineStr">
@@ -13198,7 +13210,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>45256.35721064815</v>
       </c>
       <c r="B312" t="inlineStr">
@@ -13239,7 +13251,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>45256.52245370371</v>
       </c>
       <c r="B313" t="inlineStr">
@@ -13280,7 +13292,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>45256.69059027778</v>
       </c>
       <c r="B314" t="inlineStr">
@@ -13321,7 +13333,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>45256.85734953704</v>
       </c>
       <c r="B315" t="inlineStr">
@@ -13362,7 +13374,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>45257.03400462963</v>
       </c>
       <c r="B316" t="inlineStr">
@@ -13403,7 +13415,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>45257.19155092593</v>
       </c>
       <c r="B317" t="inlineStr">
@@ -13444,7 +13456,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>45257.35650462963</v>
       </c>
       <c r="B318" t="inlineStr">
@@ -13485,7 +13497,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>45257.53321759259</v>
       </c>
       <c r="B319" t="inlineStr">
@@ -13526,7 +13538,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>45257.70081018518</v>
       </c>
       <c r="B320" t="inlineStr">
@@ -13567,7 +13579,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>45257.86366898148</v>
       </c>
       <c r="B321" t="inlineStr">
@@ -13608,7 +13620,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>45258.02313657408</v>
       </c>
       <c r="B322" t="inlineStr">
@@ -13649,7 +13661,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>45258.20119212963</v>
       </c>
       <c r="B323" t="inlineStr">
@@ -13690,7 +13702,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>45258.37204861111</v>
       </c>
       <c r="B324" t="inlineStr">
@@ -13731,7 +13743,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>45258.52905092593</v>
       </c>
       <c r="B325" t="inlineStr">
@@ -13772,7 +13784,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>45258.85935185185</v>
       </c>
       <c r="B326" t="inlineStr">
@@ -13813,7 +13825,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>45259.04449074074</v>
       </c>
       <c r="B327" t="inlineStr">
@@ -13854,7 +13866,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>45259.19268518518</v>
       </c>
       <c r="B328" t="inlineStr">
@@ -13895,7 +13907,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>45259.35609953704</v>
       </c>
       <c r="B329" t="inlineStr">
@@ -13936,7 +13948,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>45259.68962962963</v>
       </c>
       <c r="B330" t="inlineStr">
@@ -13977,7 +13989,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>45260.03945601852</v>
       </c>
       <c r="B331" t="inlineStr">
@@ -14018,7 +14030,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>45260.36225694444</v>
       </c>
       <c r="B332" t="inlineStr">
@@ -14059,7 +14071,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>45260.52806712963</v>
       </c>
       <c r="B333" t="inlineStr">
@@ -14100,7 +14112,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>45260.85832175926</v>
       </c>
       <c r="B334" t="inlineStr">
@@ -14141,7 +14153,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>45261.36832175926</v>
       </c>
       <c r="B335" t="inlineStr">
@@ -14182,7 +14194,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>45261.704375</v>
       </c>
       <c r="B336" t="inlineStr">
@@ -14223,7 +14235,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>45261.86386574074</v>
       </c>
       <c r="B337" t="inlineStr">
@@ -14264,7 +14276,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>45262.03394675926</v>
       </c>
       <c r="B338" t="inlineStr">
@@ -14305,7 +14317,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>45262.20064814815</v>
       </c>
       <c r="B339" t="inlineStr">
@@ -14346,7 +14358,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>45262.3559837963</v>
       </c>
       <c r="B340" t="inlineStr">
@@ -14387,7 +14399,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>45262.53416666666</v>
       </c>
       <c r="B341" t="inlineStr">
@@ -14428,7 +14440,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>45232.58388888889</v>
       </c>
       <c r="B342" t="inlineStr">
@@ -14469,7 +14481,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>45232.69068287037</v>
       </c>
       <c r="B343" t="inlineStr">
@@ -14510,7 +14522,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>45232.81658564815</v>
       </c>
       <c r="B344" t="inlineStr">
@@ -14551,7 +14563,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>45232.939375</v>
       </c>
       <c r="B345" t="inlineStr">
@@ -14592,7 +14604,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>45233.06450231482</v>
       </c>
       <c r="B346" t="inlineStr">
@@ -14633,7 +14645,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>45233.19976851852</v>
       </c>
       <c r="B347" t="inlineStr">
@@ -14674,7 +14686,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>45233.3163425926</v>
       </c>
       <c r="B348" t="inlineStr">
@@ -14715,7 +14727,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>45233.5778125</v>
       </c>
       <c r="B349" t="inlineStr">
@@ -14756,7 +14768,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>45233.70393518519</v>
       </c>
       <c r="B350" t="inlineStr">
@@ -14797,7 +14809,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>45233.81425925926</v>
       </c>
       <c r="B351" t="inlineStr">
@@ -14838,7 +14850,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>45233.94961805556</v>
       </c>
       <c r="B352" t="inlineStr">
@@ -14879,7 +14891,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>45234.07908564815</v>
       </c>
       <c r="B353" t="inlineStr">
@@ -14920,7 +14932,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>45234.205625</v>
       </c>
       <c r="B354" t="inlineStr">
@@ -14961,7 +14973,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>45234.32534722222</v>
       </c>
       <c r="B355" t="inlineStr">
@@ -15002,7 +15014,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>45234.44539351852</v>
       </c>
       <c r="B356" t="inlineStr">
@@ -15043,7 +15055,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>45234.57993055556</v>
       </c>
       <c r="B357" t="inlineStr">
@@ -15084,7 +15096,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>45234.69010416666</v>
       </c>
       <c r="B358" t="inlineStr">
@@ -15125,7 +15137,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>45234.8234837963</v>
       </c>
       <c r="B359" t="inlineStr">
@@ -15166,7 +15178,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>45234.94009259259</v>
       </c>
       <c r="B360" t="inlineStr">
@@ -15207,7 +15219,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>45235.07965277778</v>
       </c>
       <c r="B361" t="inlineStr">
@@ -15248,7 +15260,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>45235.1914699074</v>
       </c>
       <c r="B362" t="inlineStr">
@@ -15289,7 +15301,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>45235.31483796296</v>
       </c>
       <c r="B363" t="inlineStr">
@@ -15330,7 +15342,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>45235.4407175926</v>
       </c>
       <c r="B364" t="inlineStr">
@@ -15371,7 +15383,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>45235.56414351852</v>
       </c>
       <c r="B365" t="inlineStr">
@@ -15412,7 +15424,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>45235.70108796296</v>
       </c>
       <c r="B366" t="inlineStr">
@@ -15453,7 +15465,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>45235.81854166667</v>
       </c>
       <c r="B367" t="inlineStr">
@@ -15494,7 +15506,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>45236.22508101852</v>
       </c>
       <c r="B368" t="inlineStr">
@@ -15535,7 +15547,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>45236.31480324074</v>
       </c>
       <c r="B369" t="inlineStr">
@@ -15576,7 +15588,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>45236.44541666667</v>
       </c>
       <c r="B370" t="inlineStr">
@@ -15617,7 +15629,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>45236.6902662037</v>
       </c>
       <c r="B371" t="inlineStr">
@@ -15658,7 +15670,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>45236.81527777778</v>
       </c>
       <c r="B372" t="inlineStr">
@@ -15699,7 +15711,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>45236.9453125</v>
       </c>
       <c r="B373" t="inlineStr">
@@ -15740,7 +15752,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>45237.06493055556</v>
       </c>
       <c r="B374" t="inlineStr">
@@ -15781,7 +15793,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>45237.19125</v>
       </c>
       <c r="B375" t="inlineStr">
@@ -15822,7 +15834,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>45237.3155787037</v>
       </c>
       <c r="B376" t="inlineStr">
@@ -15863,7 +15875,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>45237.44138888889</v>
       </c>
       <c r="B377" t="inlineStr">
@@ -15904,7 +15916,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>45237.57152777778</v>
       </c>
       <c r="B378" t="inlineStr">
@@ -15945,7 +15957,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>45237.69288194444</v>
       </c>
       <c r="B379" t="inlineStr">
@@ -15986,7 +15998,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>45237.82814814815</v>
       </c>
       <c r="B380" t="inlineStr">
@@ -16027,7 +16039,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>45237.94748842593</v>
       </c>
       <c r="B381" t="inlineStr">
@@ -16068,7 +16080,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>45238.2062037037</v>
       </c>
       <c r="B382" t="inlineStr">
@@ -16109,7 +16121,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>45238.31596064815</v>
       </c>
       <c r="B383" t="inlineStr">
@@ -16150,7 +16162,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>45238.44385416667</v>
       </c>
       <c r="B384" t="inlineStr">
@@ -16191,7 +16203,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>45238.56461805556</v>
       </c>
       <c r="B385" t="inlineStr">
@@ -16232,7 +16244,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>45238.81765046297</v>
       </c>
       <c r="B386" t="inlineStr">
@@ -16273,7 +16285,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>45238.94136574074</v>
       </c>
       <c r="B387" t="inlineStr">
@@ -16314,7 +16326,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>45239.07863425926</v>
       </c>
       <c r="B388" t="inlineStr">
@@ -16355,7 +16367,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>45239.20971064815</v>
       </c>
       <c r="B389" t="inlineStr">
@@ -16396,7 +16408,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>45239.31733796297</v>
       </c>
       <c r="B390" t="inlineStr">
@@ -16437,7 +16449,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>45239.44678240741</v>
       </c>
       <c r="B391" t="inlineStr">
@@ -16478,7 +16490,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>45239.56444444445</v>
       </c>
       <c r="B392" t="inlineStr">
@@ -16519,7 +16531,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>45239.69660879629</v>
       </c>
       <c r="B393" t="inlineStr">
@@ -16560,7 +16572,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>45239.81575231482</v>
       </c>
       <c r="B394" t="inlineStr">
@@ -16601,7 +16613,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>45239.96009259259</v>
       </c>
       <c r="B395" t="inlineStr">
@@ -16642,7 +16654,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>45240.07539351852</v>
       </c>
       <c r="B396" t="inlineStr">
@@ -16683,7 +16695,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>45240.32247685185</v>
       </c>
       <c r="B397" t="inlineStr">
@@ -16724,7 +16736,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>45240.45472222222</v>
       </c>
       <c r="B398" t="inlineStr">
@@ -16765,7 +16777,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>45240.56987268518</v>
       </c>
       <c r="B399" t="inlineStr">
@@ -16806,7 +16818,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>45240.69065972222</v>
       </c>
       <c r="B400" t="inlineStr">
@@ -16847,7 +16859,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>45240.81402777778</v>
       </c>
       <c r="B401" t="inlineStr">
@@ -16888,7 +16900,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>45240.93924768519</v>
       </c>
       <c r="B402" t="inlineStr">
@@ -16929,7 +16941,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>45241.06414351852</v>
       </c>
       <c r="B403" t="inlineStr">
@@ -16970,7 +16982,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>45241.19800925926</v>
       </c>
       <c r="B404" t="inlineStr">
@@ -17011,7 +17023,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>45241.33342592593</v>
       </c>
       <c r="B405" t="inlineStr">
@@ -17052,7 +17064,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>45241.45502314815</v>
       </c>
       <c r="B406" t="inlineStr">
@@ -17093,7 +17105,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>45241.56454861111</v>
       </c>
       <c r="B407" t="inlineStr">
@@ -17134,7 +17146,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>45241.70119212963</v>
       </c>
       <c r="B408" t="inlineStr">
@@ -17175,7 +17187,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>45241.83112268519</v>
       </c>
       <c r="B409" t="inlineStr">
@@ -17216,7 +17228,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>45241.9537037037</v>
       </c>
       <c r="B410" t="inlineStr">
@@ -17257,7 +17269,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>45242.08201388889</v>
       </c>
       <c r="B411" t="inlineStr">
@@ -17298,7 +17310,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>45242.69986111111</v>
       </c>
       <c r="B412" t="inlineStr">
@@ -17339,7 +17351,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>45242.81715277778</v>
       </c>
       <c r="B413" t="inlineStr">
@@ -17380,7 +17392,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>45242.93877314815</v>
       </c>
       <c r="B414" t="inlineStr">
@@ -17421,7 +17433,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>45243.08626157408</v>
       </c>
       <c r="B415" t="inlineStr">
@@ -17462,7 +17474,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>45243.31465277778</v>
       </c>
       <c r="B416" t="inlineStr">
@@ -17503,7 +17515,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>45243.43993055556</v>
       </c>
       <c r="B417" t="inlineStr">
@@ -17544,7 +17556,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>45243.56521990741</v>
       </c>
       <c r="B418" t="inlineStr">
@@ -17585,7 +17597,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>45243.69731481482</v>
       </c>
       <c r="B419" t="inlineStr">
@@ -17626,7 +17638,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>45243.85986111111</v>
       </c>
       <c r="B420" t="inlineStr">
@@ -17667,7 +17679,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>45244.03325231482</v>
       </c>
       <c r="B421" t="inlineStr">
@@ -17708,7 +17720,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>45244.36030092592</v>
       </c>
       <c r="B422" t="inlineStr">
@@ -17749,7 +17761,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>45244.52890046296</v>
       </c>
       <c r="B423" t="inlineStr">
@@ -17790,7 +17802,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>45244.70230324074</v>
       </c>
       <c r="B424" t="inlineStr">
@@ -17831,7 +17843,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>45244.85921296296</v>
       </c>
       <c r="B425" t="inlineStr">
@@ -17872,7 +17884,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>45245.02326388889</v>
       </c>
       <c r="B426" t="inlineStr">
@@ -17913,7 +17925,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>45245.20512731482</v>
       </c>
       <c r="B427" t="inlineStr">
@@ -17954,7 +17966,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>45245.35769675926</v>
       </c>
       <c r="B428" t="inlineStr">
@@ -17995,7 +18007,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>45245.5274537037</v>
       </c>
       <c r="B429" t="inlineStr">
@@ -18036,7 +18048,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>45245.69355324074</v>
       </c>
       <c r="B430" t="inlineStr">
@@ -18077,7 +18089,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>45246.03002314815</v>
       </c>
       <c r="B431" t="inlineStr">
@@ -18118,7 +18130,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>45246.21109953704</v>
       </c>
       <c r="B432" t="inlineStr">
@@ -18159,7 +18171,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>45246.35756944444</v>
       </c>
       <c r="B433" t="inlineStr">
@@ -18200,7 +18212,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>45246.52885416667</v>
       </c>
       <c r="B434" t="inlineStr">
@@ -18241,7 +18253,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>45246.70027777777</v>
       </c>
       <c r="B435" t="inlineStr">
@@ -18282,7 +18294,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>45246.85549768519</v>
       </c>
       <c r="B436" t="inlineStr">
@@ -18323,7 +18335,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>45247.03329861111</v>
       </c>
       <c r="B437" t="inlineStr">
@@ -18364,7 +18376,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>45247.35915509259</v>
       </c>
       <c r="B438" t="inlineStr">
@@ -18405,7 +18417,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>45247.53670138889</v>
       </c>
       <c r="B439" t="inlineStr">
@@ -18446,7 +18458,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>45247.69616898148</v>
       </c>
       <c r="B440" t="inlineStr">
@@ -18487,7 +18499,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>45247.86167824074</v>
       </c>
       <c r="B441" t="inlineStr">
@@ -18528,7 +18540,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>45248.03383101852</v>
       </c>
       <c r="B442" t="inlineStr">
@@ -18569,7 +18581,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>45248.22371527777</v>
       </c>
       <c r="B443" t="inlineStr">
@@ -18610,7 +18622,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>45248.36859953704</v>
       </c>
       <c r="B444" t="inlineStr">
@@ -18651,7 +18663,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>45248.53355324074</v>
       </c>
       <c r="B445" t="inlineStr">
@@ -18692,7 +18704,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>45248.69059027778</v>
       </c>
       <c r="B446" t="inlineStr">
@@ -18733,7 +18745,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>45248.85614583334</v>
       </c>
       <c r="B447" t="inlineStr">
@@ -18774,7 +18786,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>45249.20056712963</v>
       </c>
       <c r="B448" t="inlineStr">
@@ -18815,7 +18827,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>45249.36881944445</v>
       </c>
       <c r="B449" t="inlineStr">
@@ -18856,7 +18868,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>45249.54421296297</v>
       </c>
       <c r="B450" t="inlineStr">
@@ -18897,7 +18909,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>45249.7016087963</v>
       </c>
       <c r="B451" t="inlineStr">
@@ -18938,7 +18950,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>45249.85693287037</v>
       </c>
       <c r="B452" t="inlineStr">
@@ -18979,7 +18991,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>45250.02412037037</v>
       </c>
       <c r="B453" t="inlineStr">
@@ -19020,7 +19032,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>45250.20712962963</v>
       </c>
       <c r="B454" t="inlineStr">
@@ -19061,7 +19073,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>45250.52333333333</v>
       </c>
       <c r="B455" t="inlineStr">
@@ -19102,7 +19114,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>45251.205625</v>
       </c>
       <c r="B456" t="inlineStr">
@@ -19143,7 +19155,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>45251.36144675926</v>
       </c>
       <c r="B457" t="inlineStr">
@@ -19184,7 +19196,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>45251.52275462963</v>
       </c>
       <c r="B458" t="inlineStr">
@@ -19225,7 +19237,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>45251.89483796297</v>
       </c>
       <c r="B459" t="inlineStr">
@@ -19266,7 +19278,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45252.02288194445</v>
       </c>
       <c r="B460" t="inlineStr">
@@ -19307,7 +19319,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45252.21390046296</v>
       </c>
       <c r="B461" t="inlineStr">
@@ -19348,7 +19360,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45252.52262731481</v>
       </c>
       <c r="B462" t="inlineStr">
@@ -19389,7 +19401,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45252.68975694444</v>
       </c>
       <c r="B463" t="inlineStr">
@@ -19430,7 +19442,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45253.19027777778</v>
       </c>
       <c r="B464" t="inlineStr">
@@ -19471,7 +19483,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45253.35717592593</v>
       </c>
       <c r="B465" t="inlineStr">
@@ -19512,7 +19524,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45253.52355324074</v>
       </c>
       <c r="B466" t="inlineStr">
@@ -19553,7 +19565,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45253.69</v>
       </c>
       <c r="B467" t="inlineStr">
@@ -19594,7 +19606,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45253.86288194444</v>
       </c>
       <c r="B468" t="inlineStr">
@@ -19635,7 +19647,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45254.03780092593</v>
       </c>
       <c r="B469" t="inlineStr">
@@ -19676,7 +19688,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45254.19773148148</v>
       </c>
       <c r="B470" t="inlineStr">
@@ -19717,7 +19729,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45254.35577546297</v>
       </c>
       <c r="B471" t="inlineStr">
@@ -19758,7 +19770,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45254.52780092593</v>
       </c>
       <c r="B472" t="inlineStr">
@@ -19799,7 +19811,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45254.68921296296</v>
       </c>
       <c r="B473" t="inlineStr">
@@ -19840,7 +19852,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45254.86484953704</v>
       </c>
       <c r="B474" t="inlineStr">
@@ -19881,7 +19893,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45255.03583333334</v>
       </c>
       <c r="B475" t="inlineStr">
@@ -19922,7 +19934,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45255.20597222223</v>
       </c>
       <c r="B476" t="inlineStr">
@@ -19963,7 +19975,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45255.35901620371</v>
       </c>
       <c r="B477" t="inlineStr">
@@ -20004,7 +20016,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45255.52479166666</v>
       </c>
       <c r="B478" t="inlineStr">
@@ -20045,7 +20057,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45255.68916666666</v>
       </c>
       <c r="B479" t="inlineStr">
@@ -20086,7 +20098,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45255.85908564815</v>
       </c>
       <c r="B480" t="inlineStr">
@@ -20127,7 +20139,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45256.02885416667</v>
       </c>
       <c r="B481" t="inlineStr">
@@ -20168,7 +20180,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45256.35721064815</v>
       </c>
       <c r="B482" t="inlineStr">
@@ -20209,7 +20221,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45256.52245370371</v>
       </c>
       <c r="B483" t="inlineStr">
@@ -20250,7 +20262,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45256.69059027778</v>
       </c>
       <c r="B484" t="inlineStr">
@@ -20291,7 +20303,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45256.85734953704</v>
       </c>
       <c r="B485" t="inlineStr">
@@ -20332,7 +20344,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45257.03400462963</v>
       </c>
       <c r="B486" t="inlineStr">
@@ -20373,7 +20385,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45257.19155092593</v>
       </c>
       <c r="B487" t="inlineStr">
@@ -20414,7 +20426,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45257.35650462963</v>
       </c>
       <c r="B488" t="inlineStr">
@@ -20455,7 +20467,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45257.53321759259</v>
       </c>
       <c r="B489" t="inlineStr">
@@ -20496,7 +20508,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45257.70081018518</v>
       </c>
       <c r="B490" t="inlineStr">
@@ -20537,7 +20549,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45257.86366898148</v>
       </c>
       <c r="B491" t="inlineStr">
@@ -20578,7 +20590,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45258.02313657408</v>
       </c>
       <c r="B492" t="inlineStr">
@@ -20619,7 +20631,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>45258.20119212963</v>
       </c>
       <c r="B493" t="inlineStr">
@@ -20660,7 +20672,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>45258.37204861111</v>
       </c>
       <c r="B494" t="inlineStr">
@@ -20701,7 +20713,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>45258.52905092593</v>
       </c>
       <c r="B495" t="inlineStr">
@@ -20742,7 +20754,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>45258.85935185185</v>
       </c>
       <c r="B496" t="inlineStr">
@@ -20783,7 +20795,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>45259.04449074074</v>
       </c>
       <c r="B497" t="inlineStr">
@@ -20824,7 +20836,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>45259.19268518518</v>
       </c>
       <c r="B498" t="inlineStr">
@@ -20865,7 +20877,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>45259.35609953704</v>
       </c>
       <c r="B499" t="inlineStr">
@@ -20906,7 +20918,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>45259.68962962963</v>
       </c>
       <c r="B500" t="inlineStr">
@@ -20947,7 +20959,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>45260.03945601852</v>
       </c>
       <c r="B501" t="inlineStr">
@@ -20988,7 +21000,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>45260.36225694444</v>
       </c>
       <c r="B502" t="inlineStr">
@@ -21029,7 +21041,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" s="2" t="n">
         <v>45260.52806712963</v>
       </c>
       <c r="B503" t="inlineStr">
@@ -21070,7 +21082,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" s="2" t="n">
         <v>45260.85832175926</v>
       </c>
       <c r="B504" t="inlineStr">
@@ -21111,7 +21123,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" s="2" t="n">
         <v>45261.36832175926</v>
       </c>
       <c r="B505" t="inlineStr">
@@ -21152,7 +21164,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" s="2" t="n">
         <v>45261.704375</v>
       </c>
       <c r="B506" t="inlineStr">
@@ -21193,7 +21205,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" s="2" t="n">
         <v>45261.86386574074</v>
       </c>
       <c r="B507" t="inlineStr">
@@ -21234,7 +21246,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" s="2" t="n">
         <v>45262.03394675926</v>
       </c>
       <c r="B508" t="inlineStr">
@@ -21275,7 +21287,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" s="2" t="n">
         <v>45262.20064814815</v>
       </c>
       <c r="B509" t="inlineStr">
@@ -21316,7 +21328,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" s="2" t="n">
         <v>45262.3559837963</v>
       </c>
       <c r="B510" t="inlineStr">
@@ -21357,7 +21369,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" s="2" t="n">
         <v>45262.53416666666</v>
       </c>
       <c r="B511" t="inlineStr">
@@ -21398,7 +21410,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" s="2" t="n">
         <v>45232.58388888889</v>
       </c>
       <c r="B512" t="inlineStr">
@@ -21439,7 +21451,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" s="2" t="n">
         <v>45232.69068287037</v>
       </c>
       <c r="B513" t="inlineStr">
@@ -21480,7 +21492,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" s="2" t="n">
         <v>45232.81658564815</v>
       </c>
       <c r="B514" t="inlineStr">
@@ -21521,7 +21533,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" s="2" t="n">
         <v>45232.939375</v>
       </c>
       <c r="B515" t="inlineStr">
@@ -21562,7 +21574,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" s="2" t="n">
         <v>45233.06450231482</v>
       </c>
       <c r="B516" t="inlineStr">
@@ -21603,7 +21615,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" s="2" t="n">
         <v>45233.19976851852</v>
       </c>
       <c r="B517" t="inlineStr">
@@ -21644,7 +21656,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" s="2" t="n">
         <v>45233.3163425926</v>
       </c>
       <c r="B518" t="inlineStr">
@@ -21685,7 +21697,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" s="2" t="n">
         <v>45233.5778125</v>
       </c>
       <c r="B519" t="inlineStr">
@@ -21726,7 +21738,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" s="2" t="n">
         <v>45233.70393518519</v>
       </c>
       <c r="B520" t="inlineStr">
@@ -21767,7 +21779,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" s="2" t="n">
         <v>45233.81425925926</v>
       </c>
       <c r="B521" t="inlineStr">
@@ -21808,7 +21820,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" s="2" t="n">
         <v>45233.94961805556</v>
       </c>
       <c r="B522" t="inlineStr">
@@ -21849,7 +21861,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" s="2" t="n">
         <v>45234.07908564815</v>
       </c>
       <c r="B523" t="inlineStr">
@@ -21890,7 +21902,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" s="2" t="n">
         <v>45234.205625</v>
       </c>
       <c r="B524" t="inlineStr">
@@ -21931,7 +21943,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" s="2" t="n">
         <v>45234.32534722222</v>
       </c>
       <c r="B525" t="inlineStr">
@@ -21972,7 +21984,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" s="2" t="n">
         <v>45234.44539351852</v>
       </c>
       <c r="B526" t="inlineStr">
@@ -22013,7 +22025,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" s="2" t="n">
         <v>45234.57993055556</v>
       </c>
       <c r="B527" t="inlineStr">
@@ -22054,7 +22066,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" s="2" t="n">
         <v>45234.69010416666</v>
       </c>
       <c r="B528" t="inlineStr">
@@ -22095,7 +22107,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" s="2" t="n">
         <v>45234.8234837963</v>
       </c>
       <c r="B529" t="inlineStr">
@@ -22136,7 +22148,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" s="2" t="n">
         <v>45234.94009259259</v>
       </c>
       <c r="B530" t="inlineStr">
@@ -22177,7 +22189,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" s="2" t="n">
         <v>45235.07965277778</v>
       </c>
       <c r="B531" t="inlineStr">
@@ -22218,7 +22230,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" s="2" t="n">
         <v>45235.1914699074</v>
       </c>
       <c r="B532" t="inlineStr">
@@ -22259,7 +22271,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" s="2" t="n">
         <v>45235.31483796296</v>
       </c>
       <c r="B533" t="inlineStr">
@@ -22300,7 +22312,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" s="2" t="n">
         <v>45235.4407175926</v>
       </c>
       <c r="B534" t="inlineStr">
@@ -22341,7 +22353,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" s="2" t="n">
         <v>45235.56414351852</v>
       </c>
       <c r="B535" t="inlineStr">
@@ -22382,7 +22394,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" s="2" t="n">
         <v>45235.70108796296</v>
       </c>
       <c r="B536" t="inlineStr">
@@ -22423,7 +22435,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" s="2" t="n">
         <v>45235.81854166667</v>
       </c>
       <c r="B537" t="inlineStr">
@@ -22464,7 +22476,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" s="2" t="n">
         <v>45236.22508101852</v>
       </c>
       <c r="B538" t="inlineStr">
@@ -22505,7 +22517,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" s="2" t="n">
         <v>45236.31480324074</v>
       </c>
       <c r="B539" t="inlineStr">
@@ -22546,7 +22558,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" s="2" t="n">
         <v>45236.44541666667</v>
       </c>
       <c r="B540" t="inlineStr">
@@ -22587,7 +22599,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" s="2" t="n">
         <v>45236.6902662037</v>
       </c>
       <c r="B541" t="inlineStr">
@@ -22628,7 +22640,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" s="2" t="n">
         <v>45236.81527777778</v>
       </c>
       <c r="B542" t="inlineStr">
@@ -22669,7 +22681,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" s="2" t="n">
         <v>45236.9453125</v>
       </c>
       <c r="B543" t="inlineStr">
@@ -22710,7 +22722,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" s="2" t="n">
         <v>45237.06493055556</v>
       </c>
       <c r="B544" t="inlineStr">
@@ -22751,7 +22763,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" s="2" t="n">
         <v>45237.19125</v>
       </c>
       <c r="B545" t="inlineStr">
@@ -22792,7 +22804,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" s="2" t="n">
         <v>45237.3155787037</v>
       </c>
       <c r="B546" t="inlineStr">
@@ -22833,7 +22845,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" s="2" t="n">
         <v>45237.44138888889</v>
       </c>
       <c r="B547" t="inlineStr">
@@ -22874,7 +22886,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" s="2" t="n">
         <v>45237.57152777778</v>
       </c>
       <c r="B548" t="inlineStr">
@@ -22915,7 +22927,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" s="2" t="n">
         <v>45237.69288194444</v>
       </c>
       <c r="B549" t="inlineStr">
@@ -22956,7 +22968,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" s="2" t="n">
         <v>45237.82814814815</v>
       </c>
       <c r="B550" t="inlineStr">
@@ -22997,7 +23009,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" s="2" t="n">
         <v>45237.94748842593</v>
       </c>
       <c r="B551" t="inlineStr">
@@ -23038,7 +23050,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" s="2" t="n">
         <v>45238.2062037037</v>
       </c>
       <c r="B552" t="inlineStr">
@@ -23079,7 +23091,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" s="2" t="n">
         <v>45238.31596064815</v>
       </c>
       <c r="B553" t="inlineStr">
@@ -23120,7 +23132,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" s="2" t="n">
         <v>45238.44385416667</v>
       </c>
       <c r="B554" t="inlineStr">
@@ -23161,7 +23173,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" s="2" t="n">
         <v>45238.56461805556</v>
       </c>
       <c r="B555" t="inlineStr">
@@ -23202,7 +23214,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" s="2" t="n">
         <v>45238.81765046297</v>
       </c>
       <c r="B556" t="inlineStr">
@@ -23243,7 +23255,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" s="2" t="n">
         <v>45238.94136574074</v>
       </c>
       <c r="B557" t="inlineStr">
@@ -23284,7 +23296,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" s="2" t="n">
         <v>45239.07863425926</v>
       </c>
       <c r="B558" t="inlineStr">
@@ -23325,7 +23337,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" s="2" t="n">
         <v>45239.20971064815</v>
       </c>
       <c r="B559" t="inlineStr">
@@ -23366,7 +23378,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" s="2" t="n">
         <v>45239.31733796297</v>
       </c>
       <c r="B560" t="inlineStr">
@@ -23407,7 +23419,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" s="2" t="n">
         <v>45239.44678240741</v>
       </c>
       <c r="B561" t="inlineStr">
@@ -23448,7 +23460,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" s="2" t="n">
         <v>45239.56444444445</v>
       </c>
       <c r="B562" t="inlineStr">
@@ -23489,7 +23501,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" s="2" t="n">
         <v>45239.69660879629</v>
       </c>
       <c r="B563" t="inlineStr">
@@ -23530,7 +23542,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" s="2" t="n">
         <v>45239.81575231482</v>
       </c>
       <c r="B564" t="inlineStr">
@@ -23571,7 +23583,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" s="2" t="n">
         <v>45239.96009259259</v>
       </c>
       <c r="B565" t="inlineStr">
@@ -23612,7 +23624,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" s="2" t="n">
         <v>45240.07539351852</v>
       </c>
       <c r="B566" t="inlineStr">
@@ -23653,7 +23665,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" s="2" t="n">
         <v>45240.32247685185</v>
       </c>
       <c r="B567" t="inlineStr">
@@ -23694,7 +23706,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" s="2" t="n">
         <v>45240.45472222222</v>
       </c>
       <c r="B568" t="inlineStr">
@@ -23735,7 +23747,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" s="2" t="n">
         <v>45240.56987268518</v>
       </c>
       <c r="B569" t="inlineStr">
@@ -23776,7 +23788,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" s="2" t="n">
         <v>45240.69065972222</v>
       </c>
       <c r="B570" t="inlineStr">
@@ -23817,7 +23829,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" s="2" t="n">
         <v>45240.81402777778</v>
       </c>
       <c r="B571" t="inlineStr">
@@ -23858,7 +23870,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" s="2" t="n">
         <v>45240.93924768519</v>
       </c>
       <c r="B572" t="inlineStr">
@@ -23899,7 +23911,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" s="2" t="n">
         <v>45241.06414351852</v>
       </c>
       <c r="B573" t="inlineStr">
@@ -23940,7 +23952,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" s="2" t="n">
         <v>45241.19800925926</v>
       </c>
       <c r="B574" t="inlineStr">
@@ -23981,7 +23993,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" s="2" t="n">
         <v>45241.33342592593</v>
       </c>
       <c r="B575" t="inlineStr">
@@ -24022,7 +24034,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" s="2" t="n">
         <v>45241.45502314815</v>
       </c>
       <c r="B576" t="inlineStr">
@@ -24063,7 +24075,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" s="2" t="n">
         <v>45241.56454861111</v>
       </c>
       <c r="B577" t="inlineStr">
@@ -24104,7 +24116,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" s="2" t="n">
         <v>45241.70119212963</v>
       </c>
       <c r="B578" t="inlineStr">
@@ -24145,7 +24157,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" s="2" t="n">
         <v>45241.83112268519</v>
       </c>
       <c r="B579" t="inlineStr">
@@ -24186,7 +24198,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" s="2" t="n">
         <v>45241.9537037037</v>
       </c>
       <c r="B580" t="inlineStr">
@@ -24227,7 +24239,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" s="2" t="n">
         <v>45242.08201388889</v>
       </c>
       <c r="B581" t="inlineStr">
@@ -24268,7 +24280,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" s="2" t="n">
         <v>45242.69986111111</v>
       </c>
       <c r="B582" t="inlineStr">
@@ -24309,7 +24321,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" s="2" t="n">
         <v>45242.81715277778</v>
       </c>
       <c r="B583" t="inlineStr">
@@ -24350,7 +24362,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" s="2" t="n">
         <v>45242.93877314815</v>
       </c>
       <c r="B584" t="inlineStr">
@@ -24391,7 +24403,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" s="2" t="n">
         <v>45243.08626157408</v>
       </c>
       <c r="B585" t="inlineStr">
@@ -24432,7 +24444,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" s="2" t="n">
         <v>45243.31465277778</v>
       </c>
       <c r="B586" t="inlineStr">
@@ -24473,7 +24485,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" s="2" t="n">
         <v>45243.43993055556</v>
       </c>
       <c r="B587" t="inlineStr">
@@ -24514,7 +24526,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" s="2" t="n">
         <v>45243.56521990741</v>
       </c>
       <c r="B588" t="inlineStr">
@@ -24555,7 +24567,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" s="2" t="n">
         <v>45243.69731481482</v>
       </c>
       <c r="B589" t="inlineStr">
@@ -24596,7 +24608,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" s="2" t="n">
         <v>45243.85986111111</v>
       </c>
       <c r="B590" t="inlineStr">
@@ -24637,7 +24649,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" s="2" t="n">
         <v>45244.03325231482</v>
       </c>
       <c r="B591" t="inlineStr">
@@ -24678,7 +24690,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" s="2" t="n">
         <v>45244.36030092592</v>
       </c>
       <c r="B592" t="inlineStr">
@@ -24719,7 +24731,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" s="2" t="n">
         <v>45244.52890046296</v>
       </c>
       <c r="B593" t="inlineStr">
@@ -24760,7 +24772,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" s="2" t="n">
         <v>45244.70230324074</v>
       </c>
       <c r="B594" t="inlineStr">
@@ -24801,7 +24813,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" s="2" t="n">
         <v>45244.85921296296</v>
       </c>
       <c r="B595" t="inlineStr">
@@ -24842,7 +24854,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" s="2" t="n">
         <v>45245.02326388889</v>
       </c>
       <c r="B596" t="inlineStr">
@@ -24883,7 +24895,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" s="2" t="n">
         <v>45245.20512731482</v>
       </c>
       <c r="B597" t="inlineStr">
@@ -24924,7 +24936,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" s="2" t="n">
         <v>45245.35769675926</v>
       </c>
       <c r="B598" t="inlineStr">
@@ -24965,7 +24977,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" s="2" t="n">
         <v>45245.5274537037</v>
       </c>
       <c r="B599" t="inlineStr">
@@ -25006,7 +25018,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" s="2" t="n">
         <v>45245.69355324074</v>
       </c>
       <c r="B600" t="inlineStr">
@@ -25047,7 +25059,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" s="2" t="n">
         <v>45246.03002314815</v>
       </c>
       <c r="B601" t="inlineStr">
@@ -25088,7 +25100,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" s="2" t="n">
         <v>45246.21109953704</v>
       </c>
       <c r="B602" t="inlineStr">
@@ -25129,7 +25141,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" s="2" t="n">
         <v>45246.35756944444</v>
       </c>
       <c r="B603" t="inlineStr">
@@ -25170,7 +25182,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" s="2" t="n">
         <v>45246.52885416667</v>
       </c>
       <c r="B604" t="inlineStr">
@@ -25211,7 +25223,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" s="2" t="n">
         <v>45246.70027777777</v>
       </c>
       <c r="B605" t="inlineStr">
@@ -25252,7 +25264,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" s="2" t="n">
         <v>45246.85549768519</v>
       </c>
       <c r="B606" t="inlineStr">
@@ -25293,7 +25305,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" s="2" t="n">
         <v>45247.03329861111</v>
       </c>
       <c r="B607" t="inlineStr">
@@ -25334,7 +25346,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
+      <c r="A608" s="2" t="n">
         <v>45247.35915509259</v>
       </c>
       <c r="B608" t="inlineStr">
@@ -25375,7 +25387,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
+      <c r="A609" s="2" t="n">
         <v>45247.53670138889</v>
       </c>
       <c r="B609" t="inlineStr">
@@ -25416,7 +25428,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="1" t="n">
+      <c r="A610" s="2" t="n">
         <v>45247.69616898148</v>
       </c>
       <c r="B610" t="inlineStr">
@@ -25457,7 +25469,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="1" t="n">
+      <c r="A611" s="2" t="n">
         <v>45247.86167824074</v>
       </c>
       <c r="B611" t="inlineStr">
@@ -25498,7 +25510,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="1" t="n">
+      <c r="A612" s="2" t="n">
         <v>45248.03383101852</v>
       </c>
       <c r="B612" t="inlineStr">
@@ -25539,7 +25551,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="1" t="n">
+      <c r="A613" s="2" t="n">
         <v>45248.22371527777</v>
       </c>
       <c r="B613" t="inlineStr">
@@ -25580,7 +25592,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="1" t="n">
+      <c r="A614" s="2" t="n">
         <v>45248.36859953704</v>
       </c>
       <c r="B614" t="inlineStr">
@@ -25621,7 +25633,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="1" t="n">
+      <c r="A615" s="2" t="n">
         <v>45248.53355324074</v>
       </c>
       <c r="B615" t="inlineStr">
@@ -25662,7 +25674,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="1" t="n">
+      <c r="A616" s="2" t="n">
         <v>45248.69059027778</v>
       </c>
       <c r="B616" t="inlineStr">
@@ -25703,7 +25715,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="1" t="n">
+      <c r="A617" s="2" t="n">
         <v>45248.85614583334</v>
       </c>
       <c r="B617" t="inlineStr">
@@ -25744,7 +25756,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="1" t="n">
+      <c r="A618" s="2" t="n">
         <v>45249.20056712963</v>
       </c>
       <c r="B618" t="inlineStr">
@@ -25785,7 +25797,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="1" t="n">
+      <c r="A619" s="2" t="n">
         <v>45249.36881944445</v>
       </c>
       <c r="B619" t="inlineStr">
@@ -25826,7 +25838,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="1" t="n">
+      <c r="A620" s="2" t="n">
         <v>45249.54421296297</v>
       </c>
       <c r="B620" t="inlineStr">
@@ -25867,7 +25879,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="1" t="n">
+      <c r="A621" s="2" t="n">
         <v>45249.7016087963</v>
       </c>
       <c r="B621" t="inlineStr">
@@ -25908,7 +25920,7 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="1" t="n">
+      <c r="A622" s="2" t="n">
         <v>45249.85693287037</v>
       </c>
       <c r="B622" t="inlineStr">
@@ -25949,7 +25961,7 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="1" t="n">
+      <c r="A623" s="2" t="n">
         <v>45250.02412037037</v>
       </c>
       <c r="B623" t="inlineStr">
@@ -25990,7 +26002,7 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="1" t="n">
+      <c r="A624" s="2" t="n">
         <v>45250.20712962963</v>
       </c>
       <c r="B624" t="inlineStr">
@@ -26031,7 +26043,7 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="1" t="n">
+      <c r="A625" s="2" t="n">
         <v>45250.52333333333</v>
       </c>
       <c r="B625" t="inlineStr">
@@ -26072,7 +26084,7 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" s="1" t="n">
+      <c r="A626" s="2" t="n">
         <v>45251.205625</v>
       </c>
       <c r="B626" t="inlineStr">
@@ -26113,7 +26125,7 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" s="1" t="n">
+      <c r="A627" s="2" t="n">
         <v>45251.36144675926</v>
       </c>
       <c r="B627" t="inlineStr">
@@ -26154,7 +26166,7 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" s="1" t="n">
+      <c r="A628" s="2" t="n">
         <v>45251.52275462963</v>
       </c>
       <c r="B628" t="inlineStr">
@@ -26195,7 +26207,7 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="1" t="n">
+      <c r="A629" s="2" t="n">
         <v>45251.89483796297</v>
       </c>
       <c r="B629" t="inlineStr">
@@ -26236,7 +26248,7 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="1" t="n">
+      <c r="A630" s="2" t="n">
         <v>45252.02288194445</v>
       </c>
       <c r="B630" t="inlineStr">
@@ -26277,7 +26289,7 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" s="1" t="n">
+      <c r="A631" s="2" t="n">
         <v>45252.21390046296</v>
       </c>
       <c r="B631" t="inlineStr">
@@ -26318,7 +26330,7 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="1" t="n">
+      <c r="A632" s="2" t="n">
         <v>45252.52262731481</v>
       </c>
       <c r="B632" t="inlineStr">
@@ -26359,7 +26371,7 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="1" t="n">
+      <c r="A633" s="2" t="n">
         <v>45252.68975694444</v>
       </c>
       <c r="B633" t="inlineStr">
@@ -26400,7 +26412,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="1" t="n">
+      <c r="A634" s="2" t="n">
         <v>45253.19027777778</v>
       </c>
       <c r="B634" t="inlineStr">
@@ -26441,7 +26453,7 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" s="1" t="n">
+      <c r="A635" s="2" t="n">
         <v>45253.35717592593</v>
       </c>
       <c r="B635" t="inlineStr">
@@ -26482,7 +26494,7 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" s="1" t="n">
+      <c r="A636" s="2" t="n">
         <v>45253.52355324074</v>
       </c>
       <c r="B636" t="inlineStr">
@@ -26523,7 +26535,7 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="1" t="n">
+      <c r="A637" s="2" t="n">
         <v>45253.69</v>
       </c>
       <c r="B637" t="inlineStr">
@@ -26564,7 +26576,7 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" s="1" t="n">
+      <c r="A638" s="2" t="n">
         <v>45253.86288194444</v>
       </c>
       <c r="B638" t="inlineStr">
@@ -26605,7 +26617,7 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" s="1" t="n">
+      <c r="A639" s="2" t="n">
         <v>45254.03780092593</v>
       </c>
       <c r="B639" t="inlineStr">
@@ -26646,7 +26658,7 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" s="1" t="n">
+      <c r="A640" s="2" t="n">
         <v>45254.19773148148</v>
       </c>
       <c r="B640" t="inlineStr">
@@ -26687,7 +26699,7 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" s="1" t="n">
+      <c r="A641" s="2" t="n">
         <v>45254.35577546297</v>
       </c>
       <c r="B641" t="inlineStr">
@@ -26728,7 +26740,7 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" s="1" t="n">
+      <c r="A642" s="2" t="n">
         <v>45254.52780092593</v>
       </c>
       <c r="B642" t="inlineStr">
@@ -26769,7 +26781,7 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" s="1" t="n">
+      <c r="A643" s="2" t="n">
         <v>45254.68921296296</v>
       </c>
       <c r="B643" t="inlineStr">
@@ -26810,7 +26822,7 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" s="1" t="n">
+      <c r="A644" s="2" t="n">
         <v>45254.86484953704</v>
       </c>
       <c r="B644" t="inlineStr">
@@ -26851,7 +26863,7 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" s="1" t="n">
+      <c r="A645" s="2" t="n">
         <v>45255.03583333334</v>
       </c>
       <c r="B645" t="inlineStr">
@@ -26892,7 +26904,7 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" s="1" t="n">
+      <c r="A646" s="2" t="n">
         <v>45255.20597222223</v>
       </c>
       <c r="B646" t="inlineStr">
@@ -26933,7 +26945,7 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" s="1" t="n">
+      <c r="A647" s="2" t="n">
         <v>45255.35901620371</v>
       </c>
       <c r="B647" t="inlineStr">
@@ -26974,7 +26986,7 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="1" t="n">
+      <c r="A648" s="2" t="n">
         <v>45255.52479166666</v>
       </c>
       <c r="B648" t="inlineStr">
@@ -27015,7 +27027,7 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" s="1" t="n">
+      <c r="A649" s="2" t="n">
         <v>45255.68916666666</v>
       </c>
       <c r="B649" t="inlineStr">
@@ -27056,7 +27068,7 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" s="1" t="n">
+      <c r="A650" s="2" t="n">
         <v>45255.85908564815</v>
       </c>
       <c r="B650" t="inlineStr">
@@ -27097,7 +27109,7 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" s="1" t="n">
+      <c r="A651" s="2" t="n">
         <v>45256.02885416667</v>
       </c>
       <c r="B651" t="inlineStr">
@@ -27138,7 +27150,7 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="1" t="n">
+      <c r="A652" s="2" t="n">
         <v>45256.35721064815</v>
       </c>
       <c r="B652" t="inlineStr">
@@ -27179,7 +27191,7 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="1" t="n">
+      <c r="A653" s="2" t="n">
         <v>45256.52245370371</v>
       </c>
       <c r="B653" t="inlineStr">
@@ -27220,7 +27232,7 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" s="1" t="n">
+      <c r="A654" s="2" t="n">
         <v>45256.69059027778</v>
       </c>
       <c r="B654" t="inlineStr">
@@ -27261,7 +27273,7 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="1" t="n">
+      <c r="A655" s="2" t="n">
         <v>45256.85734953704</v>
       </c>
       <c r="B655" t="inlineStr">
@@ -27302,7 +27314,7 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" s="1" t="n">
+      <c r="A656" s="2" t="n">
         <v>45257.03400462963</v>
       </c>
       <c r="B656" t="inlineStr">
@@ -27343,7 +27355,7 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" s="1" t="n">
+      <c r="A657" s="2" t="n">
         <v>45257.19155092593</v>
       </c>
       <c r="B657" t="inlineStr">
@@ -27384,7 +27396,7 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" s="1" t="n">
+      <c r="A658" s="2" t="n">
         <v>45257.35650462963</v>
       </c>
       <c r="B658" t="inlineStr">
@@ -27425,7 +27437,7 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" s="1" t="n">
+      <c r="A659" s="2" t="n">
         <v>45257.53321759259</v>
       </c>
       <c r="B659" t="inlineStr">
@@ -27466,7 +27478,7 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" s="1" t="n">
+      <c r="A660" s="2" t="n">
         <v>45257.70081018518</v>
       </c>
       <c r="B660" t="inlineStr">
@@ -27507,7 +27519,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" s="1" t="n">
+      <c r="A661" s="2" t="n">
         <v>45257.86366898148</v>
       </c>
       <c r="B661" t="inlineStr">
@@ -27548,7 +27560,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" s="1" t="n">
+      <c r="A662" s="2" t="n">
         <v>45258.02313657408</v>
       </c>
       <c r="B662" t="inlineStr">
@@ -27589,7 +27601,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" s="1" t="n">
+      <c r="A663" s="2" t="n">
         <v>45258.20119212963</v>
       </c>
       <c r="B663" t="inlineStr">
@@ -27630,7 +27642,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" s="1" t="n">
+      <c r="A664" s="2" t="n">
         <v>45258.37204861111</v>
       </c>
       <c r="B664" t="inlineStr">
@@ -27671,7 +27683,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" s="1" t="n">
+      <c r="A665" s="2" t="n">
         <v>45258.52905092593</v>
       </c>
       <c r="B665" t="inlineStr">
@@ -27712,7 +27724,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" s="1" t="n">
+      <c r="A666" s="2" t="n">
         <v>45258.85935185185</v>
       </c>
       <c r="B666" t="inlineStr">
@@ -27753,7 +27765,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" s="1" t="n">
+      <c r="A667" s="2" t="n">
         <v>45259.04449074074</v>
       </c>
       <c r="B667" t="inlineStr">
@@ -27794,7 +27806,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" s="1" t="n">
+      <c r="A668" s="2" t="n">
         <v>45259.19268518518</v>
       </c>
       <c r="B668" t="inlineStr">
@@ -27835,7 +27847,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" s="1" t="n">
+      <c r="A669" s="2" t="n">
         <v>45259.35609953704</v>
       </c>
       <c r="B669" t="inlineStr">
@@ -27876,7 +27888,7 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" s="1" t="n">
+      <c r="A670" s="2" t="n">
         <v>45259.68962962963</v>
       </c>
       <c r="B670" t="inlineStr">
@@ -27917,7 +27929,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" s="1" t="n">
+      <c r="A671" s="2" t="n">
         <v>45260.03945601852</v>
       </c>
       <c r="B671" t="inlineStr">
@@ -27958,7 +27970,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" s="1" t="n">
+      <c r="A672" s="2" t="n">
         <v>45260.36225694444</v>
       </c>
       <c r="B672" t="inlineStr">
@@ -27999,7 +28011,7 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" s="1" t="n">
+      <c r="A673" s="2" t="n">
         <v>45260.52806712963</v>
       </c>
       <c r="B673" t="inlineStr">
@@ -28040,7 +28052,7 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" s="1" t="n">
+      <c r="A674" s="2" t="n">
         <v>45260.85832175926</v>
       </c>
       <c r="B674" t="inlineStr">
@@ -28081,7 +28093,7 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" s="1" t="n">
+      <c r="A675" s="2" t="n">
         <v>45261.36832175926</v>
       </c>
       <c r="B675" t="inlineStr">
@@ -28122,7 +28134,7 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" s="1" t="n">
+      <c r="A676" s="2" t="n">
         <v>45261.704375</v>
       </c>
       <c r="B676" t="inlineStr">
@@ -28163,7 +28175,7 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" s="1" t="n">
+      <c r="A677" s="2" t="n">
         <v>45261.86386574074</v>
       </c>
       <c r="B677" t="inlineStr">
@@ -28204,7 +28216,7 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" s="1" t="n">
+      <c r="A678" s="2" t="n">
         <v>45262.03394675926</v>
       </c>
       <c r="B678" t="inlineStr">
@@ -28245,7 +28257,7 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" s="1" t="n">
+      <c r="A679" s="2" t="n">
         <v>45262.20064814815</v>
       </c>
       <c r="B679" t="inlineStr">
@@ -28286,7 +28298,7 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" s="1" t="n">
+      <c r="A680" s="2" t="n">
         <v>45262.3559837963</v>
       </c>
       <c r="B680" t="inlineStr">
@@ -28327,7 +28339,7 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="1" t="n">
+      <c r="A681" s="2" t="n">
         <v>45262.53416666666</v>
       </c>
       <c r="B681" t="inlineStr">
